--- a/requirements/requirements.xlsx
+++ b/requirements/requirements.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="1" r:id="Rd7a5f169c2994de4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="Rabdbe7ec273e4ddc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Matrix" sheetId="3" r:id="R15bde2290ad04e18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="1" r:id="R79986d8225864e45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R6edd2277e81743f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Matrix" sheetId="3" r:id="R5714cca68ef141b1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -562,21 +562,21 @@
   <x:dxfs count="3">
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -1899,7 +1899,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98e4382646514def"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R035b24ae34894914"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1932,7 +1932,7 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
-        <x:v>Verification Planning</x:v>
+        <x:v>Verification Summary</x:v>
       </x:c>
       <x:c r="E3" s="24" t="str">
         <x:v>Value</x:v>
@@ -1963,7 +1963,7 @@
         <x:v>Verification Status</x:v>
       </x:c>
       <x:c r="E5" t="str">
-        <x:v>Planning - Execution Pending</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1977,7 +1977,7 @@
         <x:v>Test Execution</x:v>
       </x:c>
       <x:c r="E6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>95 PASS / 0 FAIL</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1987,7 +1987,7 @@
         <x:v>Evidence</x:v>
       </x:c>
       <x:c r="E7" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-001 to RESULT-031</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1998,10 +1998,10 @@
         <x:v>139</x:v>
       </x:c>
       <x:c r="D8" t="str">
-        <x:v>Matrix Sheet</x:v>
+        <x:v>Execution Environment</x:v>
       </x:c>
       <x:c r="E8" t="str">
-        <x:v>Verification Matrix</x:v>
+        <x:v>Windows / Python 3.14.2 / pytest 9.1.1</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -2145,13 +2145,13 @@
         <x:v>TC-INP-001</x:v>
       </x:c>
       <x:c r="F2" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G2" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-001</x:v>
       </x:c>
       <x:c r="H2" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I2" s="23" t="str">
         <x:v>Draft</x:v>
@@ -2160,7 +2160,7 @@
         <x:v>SN-DEV-002</x:v>
       </x:c>
       <x:c r="K2" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -2180,13 +2180,13 @@
         <x:v>TC-INP-001</x:v>
       </x:c>
       <x:c r="F3" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G3" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-001</x:v>
       </x:c>
       <x:c r="H3" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I3" s="23" t="str">
         <x:v>Draft</x:v>
@@ -2195,7 +2195,7 @@
         <x:v>Project Scope</x:v>
       </x:c>
       <x:c r="K3" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2215,13 +2215,13 @@
         <x:v>TC-INP-001</x:v>
       </x:c>
       <x:c r="F4" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G4" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-001</x:v>
       </x:c>
       <x:c r="H4" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I4" s="23" t="str">
         <x:v>Draft</x:v>
@@ -2230,7 +2230,7 @@
         <x:v>Project Scope</x:v>
       </x:c>
       <x:c r="K4" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2250,13 +2250,13 @@
         <x:v>TC-INP-001</x:v>
       </x:c>
       <x:c r="F5" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G5" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-001</x:v>
       </x:c>
       <x:c r="H5" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I5" s="23" t="str">
         <x:v>Draft</x:v>
@@ -2265,7 +2265,7 @@
         <x:v>Project Scope</x:v>
       </x:c>
       <x:c r="K5" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2285,13 +2285,13 @@
         <x:v>TC-INP-001</x:v>
       </x:c>
       <x:c r="F6" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G6" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-001</x:v>
       </x:c>
       <x:c r="H6" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I6" s="23" t="str">
         <x:v>Draft</x:v>
@@ -2300,7 +2300,7 @@
         <x:v>Project Scope</x:v>
       </x:c>
       <x:c r="K6" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2320,13 +2320,13 @@
         <x:v>TC-INP-001</x:v>
       </x:c>
       <x:c r="F7" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G7" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-001</x:v>
       </x:c>
       <x:c r="H7" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I7" s="23" t="str">
         <x:v>Draft</x:v>
@@ -2335,7 +2335,7 @@
         <x:v>Project Scope</x:v>
       </x:c>
       <x:c r="K7" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2355,13 +2355,13 @@
         <x:v>TC-INP-002</x:v>
       </x:c>
       <x:c r="F8" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G8" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-002</x:v>
       </x:c>
       <x:c r="H8" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I8" s="23" t="str">
         <x:v>Draft</x:v>
@@ -2370,7 +2370,7 @@
         <x:v>SN-SRV-002</x:v>
       </x:c>
       <x:c r="K8" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -2387,16 +2387,16 @@
         <x:v>Test</x:v>
       </x:c>
       <x:c r="E9" s="23" t="str">
-        <x:v>TC-VAL-001</x:v>
+        <x:v>TC-VAL-001; TC-VAL-006</x:v>
       </x:c>
       <x:c r="F9" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G9" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-003; RESULT-008</x:v>
       </x:c>
       <x:c r="H9" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I9" s="23" t="str">
         <x:v>Draft</x:v>
@@ -2405,7 +2405,7 @@
         <x:v>SN-DRV-003; SN-SRV-003</x:v>
       </x:c>
       <x:c r="K9" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -2425,13 +2425,13 @@
         <x:v>TC-VAL-002</x:v>
       </x:c>
       <x:c r="F10" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G10" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-004</x:v>
       </x:c>
       <x:c r="H10" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I10" s="23" t="str">
         <x:v>Draft</x:v>
@@ -2440,7 +2440,7 @@
         <x:v>SN-SRV-003</x:v>
       </x:c>
       <x:c r="K10" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -2460,13 +2460,13 @@
         <x:v>TC-VAL-003</x:v>
       </x:c>
       <x:c r="F11" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G11" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-005</x:v>
       </x:c>
       <x:c r="H11" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I11" s="23" t="str">
         <x:v>Draft</x:v>
@@ -2475,7 +2475,7 @@
         <x:v>SN-DEV-002; SN-TST-002</x:v>
       </x:c>
       <x:c r="K11" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -2495,13 +2495,13 @@
         <x:v>TC-VAL-001; TC-VAL-004; TC-VAL-005; TC-VAL-006</x:v>
       </x:c>
       <x:c r="F12" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G12" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-003; RESULT-006; RESULT-007; RESULT-008</x:v>
       </x:c>
       <x:c r="H12" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I12" s="23" t="str">
         <x:v>Draft</x:v>
@@ -2510,7 +2510,7 @@
         <x:v>SN-DRV-003; SN-SRV-003</x:v>
       </x:c>
       <x:c r="K12" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -2530,13 +2530,13 @@
         <x:v>TC-VAL-002; TC-VAL-003; TC-VAL-004; TC-VAL-005</x:v>
       </x:c>
       <x:c r="F13" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G13" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-004; RESULT-005; RESULT-006; RESULT-007</x:v>
       </x:c>
       <x:c r="H13" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I13" s="23" t="str">
         <x:v>Draft</x:v>
@@ -2545,7 +2545,7 @@
         <x:v>SN-SRV-003</x:v>
       </x:c>
       <x:c r="K13" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -2565,13 +2565,13 @@
         <x:v>TC-VAL-002; TC-VAL-003; TC-VAL-004; TC-VAL-005</x:v>
       </x:c>
       <x:c r="F14" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G14" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-004; RESULT-005; RESULT-006; RESULT-007</x:v>
       </x:c>
       <x:c r="H14" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I14" s="23" t="str">
         <x:v>Draft</x:v>
@@ -2580,7 +2580,7 @@
         <x:v>SN-DRV-003; SN-SRV-003</x:v>
       </x:c>
       <x:c r="K14" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -2600,13 +2600,13 @@
         <x:v>TC-MON-001; TC-MON-002</x:v>
       </x:c>
       <x:c r="F15" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G15" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-009; RESULT-010</x:v>
       </x:c>
       <x:c r="H15" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I15" s="23" t="str">
         <x:v>Draft</x:v>
@@ -2615,7 +2615,7 @@
         <x:v>Project Scope</x:v>
       </x:c>
       <x:c r="K15" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2632,16 +2632,16 @@
         <x:v>Test</x:v>
       </x:c>
       <x:c r="E16" s="23" t="str">
-        <x:v>TC-MON-001</x:v>
+        <x:v>TC-MON-001; TC-MON-002</x:v>
       </x:c>
       <x:c r="F16" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G16" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-009; RESULT-010</x:v>
       </x:c>
       <x:c r="H16" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I16" s="23" t="str">
         <x:v>Draft</x:v>
@@ -2650,7 +2650,7 @@
         <x:v>Project Scope</x:v>
       </x:c>
       <x:c r="K16" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -2667,16 +2667,16 @@
         <x:v>Test</x:v>
       </x:c>
       <x:c r="E17" s="23" t="str">
-        <x:v>TC-MON-001</x:v>
+        <x:v>TC-MON-001; TC-MON-002</x:v>
       </x:c>
       <x:c r="F17" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G17" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-009; RESULT-010</x:v>
       </x:c>
       <x:c r="H17" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I17" s="23" t="str">
         <x:v>Draft</x:v>
@@ -2685,7 +2685,7 @@
         <x:v>Project Scope</x:v>
       </x:c>
       <x:c r="K17" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -2702,16 +2702,16 @@
         <x:v>Test</x:v>
       </x:c>
       <x:c r="E18" s="23" t="str">
-        <x:v>TC-MON-001</x:v>
+        <x:v>TC-MON-001; TC-MON-002</x:v>
       </x:c>
       <x:c r="F18" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G18" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-009; RESULT-010</x:v>
       </x:c>
       <x:c r="H18" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I18" s="23" t="str">
         <x:v>Draft</x:v>
@@ -2720,7 +2720,7 @@
         <x:v>Project Scope</x:v>
       </x:c>
       <x:c r="K18" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -2737,16 +2737,16 @@
         <x:v>Test</x:v>
       </x:c>
       <x:c r="E19" s="23" t="str">
-        <x:v>TC-MON-001</x:v>
+        <x:v>TC-MON-001; TC-MON-002</x:v>
       </x:c>
       <x:c r="F19" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G19" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-009; RESULT-010</x:v>
       </x:c>
       <x:c r="H19" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I19" s="23" t="str">
         <x:v>Draft</x:v>
@@ -2755,7 +2755,7 @@
         <x:v>Project Scope</x:v>
       </x:c>
       <x:c r="K19" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -2772,16 +2772,16 @@
         <x:v>Test</x:v>
       </x:c>
       <x:c r="E20" s="23" t="str">
-        <x:v>TC-MON-001</x:v>
+        <x:v>TC-MON-001; TC-MON-002</x:v>
       </x:c>
       <x:c r="F20" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G20" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-009; RESULT-010</x:v>
       </x:c>
       <x:c r="H20" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I20" s="23" t="str">
         <x:v>Draft</x:v>
@@ -2790,7 +2790,7 @@
         <x:v>Project Scope</x:v>
       </x:c>
       <x:c r="K20" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -2810,13 +2810,13 @@
         <x:v>TC-MON-002; TC-DIAG-002</x:v>
       </x:c>
       <x:c r="F21" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G21" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-010; RESULT-012</x:v>
       </x:c>
       <x:c r="H21" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I21" s="23" t="str">
         <x:v>Draft</x:v>
@@ -2825,7 +2825,7 @@
         <x:v>SN-DRV-001; SN-SRV-001</x:v>
       </x:c>
       <x:c r="K21" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -2845,13 +2845,13 @@
         <x:v>TC-DIAG-001</x:v>
       </x:c>
       <x:c r="F22" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G22" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-011</x:v>
       </x:c>
       <x:c r="H22" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I22" s="23" t="str">
         <x:v>Draft</x:v>
@@ -2860,7 +2860,7 @@
         <x:v>SN-DRV-004</x:v>
       </x:c>
       <x:c r="K22" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -2880,13 +2880,13 @@
         <x:v>TC-DIAG-002</x:v>
       </x:c>
       <x:c r="F23" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G23" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-012</x:v>
       </x:c>
       <x:c r="H23" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I23" s="23" t="str">
         <x:v>Draft</x:v>
@@ -2895,7 +2895,7 @@
         <x:v>SN-SRV-001</x:v>
       </x:c>
       <x:c r="K23" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -2915,13 +2915,13 @@
         <x:v>TC-DIAG-003</x:v>
       </x:c>
       <x:c r="F24" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G24" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-013</x:v>
       </x:c>
       <x:c r="H24" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I24" s="23" t="str">
         <x:v>Draft</x:v>
@@ -2930,7 +2930,7 @@
         <x:v>Engineering Requirement</x:v>
       </x:c>
       <x:c r="K24" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -2950,13 +2950,13 @@
         <x:v>TC-DIAG-004</x:v>
       </x:c>
       <x:c r="F25" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G25" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-014</x:v>
       </x:c>
       <x:c r="H25" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I25" s="23" t="str">
         <x:v>Draft</x:v>
@@ -2965,7 +2965,7 @@
         <x:v>Engineering Requirement</x:v>
       </x:c>
       <x:c r="K25" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -2985,13 +2985,13 @@
         <x:v>TC-SEV-002; TC-SEV-003; TC-SEV-004</x:v>
       </x:c>
       <x:c r="F26" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G26" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-016; RESULT-017; RESULT-018</x:v>
       </x:c>
       <x:c r="H26" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I26" s="23" t="str">
         <x:v>Draft</x:v>
@@ -3000,7 +3000,7 @@
         <x:v>SN-DRV-002; SN-SRV-002</x:v>
       </x:c>
       <x:c r="K26" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -3020,13 +3020,13 @@
         <x:v>TC-SEV-001; TC-SEV-002; TC-SEV-003; TC-SEV-004</x:v>
       </x:c>
       <x:c r="F27" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G27" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-015; RESULT-016; RESULT-017; RESULT-018</x:v>
       </x:c>
       <x:c r="H27" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I27" s="23" t="str">
         <x:v>Draft</x:v>
@@ -3035,7 +3035,7 @@
         <x:v>SN-DRV-002; SN-DRV-004</x:v>
       </x:c>
       <x:c r="K27" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -3055,13 +3055,13 @@
         <x:v>TC-SEV-001</x:v>
       </x:c>
       <x:c r="F28" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G28" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-015</x:v>
       </x:c>
       <x:c r="H28" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I28" s="23" t="str">
         <x:v>Draft</x:v>
@@ -3070,7 +3070,7 @@
         <x:v>SN-DRV-004</x:v>
       </x:c>
       <x:c r="K28" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -3090,13 +3090,13 @@
         <x:v>TC-SEV-002; TC-SEV-003; TC-SEV-004</x:v>
       </x:c>
       <x:c r="F29" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G29" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-016; RESULT-017; RESULT-018</x:v>
       </x:c>
       <x:c r="H29" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I29" s="23" t="str">
         <x:v>Draft</x:v>
@@ -3105,7 +3105,7 @@
         <x:v>SN-DRV-002; SN-DEV-003</x:v>
       </x:c>
       <x:c r="K29" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -3125,13 +3125,13 @@
         <x:v>TC-SEV-005</x:v>
       </x:c>
       <x:c r="F30" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G30" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-019</x:v>
       </x:c>
       <x:c r="H30" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I30" s="23" t="str">
         <x:v>Draft</x:v>
@@ -3140,7 +3140,7 @@
         <x:v>Engineering Requirement</x:v>
       </x:c>
       <x:c r="K30" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -3160,13 +3160,13 @@
         <x:v>TC-WRN-001; TC-WRN-002</x:v>
       </x:c>
       <x:c r="F31" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G31" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-020; RESULT-021</x:v>
       </x:c>
       <x:c r="H31" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I31" s="23" t="str">
         <x:v>Draft</x:v>
@@ -3175,7 +3175,7 @@
         <x:v>SN-DRV-001</x:v>
       </x:c>
       <x:c r="K31" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -3195,13 +3195,13 @@
         <x:v>TC-WRN-001</x:v>
       </x:c>
       <x:c r="F32" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G32" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-020</x:v>
       </x:c>
       <x:c r="H32" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I32" s="23" t="str">
         <x:v>Draft</x:v>
@@ -3210,7 +3210,7 @@
         <x:v>SN-DRV-002</x:v>
       </x:c>
       <x:c r="K32" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -3230,13 +3230,13 @@
         <x:v>TC-WRN-001</x:v>
       </x:c>
       <x:c r="F33" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G33" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-020</x:v>
       </x:c>
       <x:c r="H33" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I33" s="23" t="str">
         <x:v>Draft</x:v>
@@ -3245,7 +3245,7 @@
         <x:v>SN-DRV-001</x:v>
       </x:c>
       <x:c r="K33" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -3265,13 +3265,13 @@
         <x:v>TC-WRN-001</x:v>
       </x:c>
       <x:c r="F34" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G34" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-020</x:v>
       </x:c>
       <x:c r="H34" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I34" s="23" t="str">
         <x:v>Draft</x:v>
@@ -3280,7 +3280,7 @@
         <x:v>SN-DRV-002</x:v>
       </x:c>
       <x:c r="K34" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -3300,13 +3300,13 @@
         <x:v>TC-WRN-003</x:v>
       </x:c>
       <x:c r="F35" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G35" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-022</x:v>
       </x:c>
       <x:c r="H35" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I35" s="23" t="str">
         <x:v>Draft</x:v>
@@ -3315,7 +3315,7 @@
         <x:v>SN-DRV-004</x:v>
       </x:c>
       <x:c r="K35" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -3335,13 +3335,13 @@
         <x:v>TC-EVT-001</x:v>
       </x:c>
       <x:c r="F36" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G36" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-023</x:v>
       </x:c>
       <x:c r="H36" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I36" s="23" t="str">
         <x:v>Draft</x:v>
@@ -3350,7 +3350,7 @@
         <x:v>SN-SRV-001; SN-SRV-002</x:v>
       </x:c>
       <x:c r="K36" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -3370,13 +3370,13 @@
         <x:v>TC-EVT-001</x:v>
       </x:c>
       <x:c r="F37" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G37" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-023</x:v>
       </x:c>
       <x:c r="H37" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I37" s="23" t="str">
         <x:v>Draft</x:v>
@@ -3385,7 +3385,7 @@
         <x:v>SN-SRV-004</x:v>
       </x:c>
       <x:c r="K37" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -3405,13 +3405,13 @@
         <x:v>TC-EVT-001</x:v>
       </x:c>
       <x:c r="F38" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G38" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-023</x:v>
       </x:c>
       <x:c r="H38" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I38" s="23" t="str">
         <x:v>Draft</x:v>
@@ -3420,7 +3420,7 @@
         <x:v>SN-SRV-001</x:v>
       </x:c>
       <x:c r="K38" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -3440,13 +3440,13 @@
         <x:v>TC-EVT-001</x:v>
       </x:c>
       <x:c r="F39" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G39" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-023</x:v>
       </x:c>
       <x:c r="H39" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I39" s="23" t="str">
         <x:v>Draft</x:v>
@@ -3455,7 +3455,7 @@
         <x:v>SN-SRV-002</x:v>
       </x:c>
       <x:c r="K39" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -3475,13 +3475,13 @@
         <x:v>TC-EVT-001</x:v>
       </x:c>
       <x:c r="F40" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G40" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-023</x:v>
       </x:c>
       <x:c r="H40" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I40" s="23" t="str">
         <x:v>Draft</x:v>
@@ -3490,7 +3490,7 @@
         <x:v>SN-SRV-002</x:v>
       </x:c>
       <x:c r="K40" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -3510,13 +3510,13 @@
         <x:v>TC-EVT-001</x:v>
       </x:c>
       <x:c r="F41" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G41" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-023</x:v>
       </x:c>
       <x:c r="H41" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I41" s="23" t="str">
         <x:v>Draft</x:v>
@@ -3525,7 +3525,7 @@
         <x:v>SN-SRV-002</x:v>
       </x:c>
       <x:c r="K41" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -3545,13 +3545,13 @@
         <x:v>TC-EVT-002</x:v>
       </x:c>
       <x:c r="F42" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G42" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-024</x:v>
       </x:c>
       <x:c r="H42" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I42" s="23" t="str">
         <x:v>Draft</x:v>
@@ -3560,7 +3560,7 @@
         <x:v>SN-SRV-003</x:v>
       </x:c>
       <x:c r="K42" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -3580,13 +3580,13 @@
         <x:v>TC-CFG-001; TC-CFG-002</x:v>
       </x:c>
       <x:c r="F43" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G43" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-025; RESULT-026</x:v>
       </x:c>
       <x:c r="H43" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I43" s="23" t="str">
         <x:v>Draft</x:v>
@@ -3595,7 +3595,7 @@
         <x:v>SN-DEV-003</x:v>
       </x:c>
       <x:c r="K43" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -3615,13 +3615,13 @@
         <x:v>TC-CFG-001; TC-CFG-002; TC-CFG-003</x:v>
       </x:c>
       <x:c r="F44" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G44" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-025; RESULT-026; RESULT-027</x:v>
       </x:c>
       <x:c r="H44" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I44" s="23" t="str">
         <x:v>Draft</x:v>
@@ -3630,7 +3630,7 @@
         <x:v>SN-DEV-003</x:v>
       </x:c>
       <x:c r="K44" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -3650,13 +3650,13 @@
         <x:v>TC-CFG-001</x:v>
       </x:c>
       <x:c r="F45" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G45" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-025</x:v>
       </x:c>
       <x:c r="H45" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I45" s="23" t="str">
         <x:v>Draft</x:v>
@@ -3665,7 +3665,7 @@
         <x:v>SN-DEV-003; SN-TST-002</x:v>
       </x:c>
       <x:c r="K45" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -3685,13 +3685,13 @@
         <x:v>TC-CFG-002</x:v>
       </x:c>
       <x:c r="F46" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G46" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-026</x:v>
       </x:c>
       <x:c r="H46" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I46" s="23" t="str">
         <x:v>Draft</x:v>
@@ -3700,7 +3700,7 @@
         <x:v>SN-DEV-003</x:v>
       </x:c>
       <x:c r="K46" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -3720,13 +3720,13 @@
         <x:v>TC-CFG-003</x:v>
       </x:c>
       <x:c r="F47" s="23" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G47" s="23" t="str">
-        <x:v>TBD</x:v>
+        <x:v>RESULT-027</x:v>
       </x:c>
       <x:c r="H47" s="23" t="str">
-        <x:v>NOT VERIFIED</x:v>
+        <x:v>VERIFIED</x:v>
       </x:c>
       <x:c r="I47" s="23" t="str">
         <x:v>Draft</x:v>
@@ -3735,7 +3735,7 @@
         <x:v>Engineering Requirement</x:v>
       </x:c>
       <x:c r="K47" s="23" t="str">
-        <x:v>Planned verification - execution pending prototype implementation.</x:v>
+        <x:v>Verification completed. Evidence recorded from executed VehicleGuard V1 pytest verification.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
